--- a/peer review 8/Rubric_Group9_peer_review_DRAFT_v1.xlsx
+++ b/peer review 8/Rubric_Group9_peer_review_DRAFT_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b1e3e05317db2af/Bureaublad/Obsidian/Code-Project/JADS Courses/Process Mining/peer review 8/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_8C25F1923C57F6D38E6E51DCA8A7D8D6839295F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_8C25F1923C57F6D38E6E51DCA8A7D8D6839295F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE0BB4CC-3DF9-4EB4-9FEB-A407676C0F34}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -144,11 +144,6 @@
     <t xml:space="preserve">Relevant implementation details are provided to complement the description of the conceptual approach in order to ensure reproducibility. This description matches the actual implementation. Note that the implementation as such is graded separately. </t>
   </si>
   <si>
-    <t>Note: we only had the paper, not the code, so we could check completeness and internal consistency, not whether it matches the implementation.
-Strengths: Very good reproducibility detail. Python version, uv with pyproject.toml, a package table with versions, the module structure (model pipeline, llm pipeline, jev pipeline) and one notebook per rule. Seeds (42), temperature 0, context window 32,768 tokens with a check that the server uses it, max 800 tokens, 120 s timeout, three retries, and the fallback label when no answer can be parsed (115 of 12,084) are all given. Split and prefix counts (914/229 cases, 3,401/1,007 prefixes) and the diagonal covariance choice with its reason are clear, and Appendix A contains the prompt.
-Improvements: (1) Say in which order to run the notebooks, where the BPIC 2011 file is expected, and how long a full run takes. (2) Mention the hardware or server behind Ollama, and note that temperature 0 on a remote server is not guaranteed to give identical output across machines. (3) Say how the JEV API is accessed (key, cost, availability), since this limits reproducibility for others. (4) Clarify typesafe-sdk 0.7.4 (package) versus jev-1.13.0 (model version) in one line. (5) Small typo in 3.3: 'removed form all cases'.</t>
-  </si>
-  <si>
     <t>S4</t>
   </si>
   <si>
@@ -238,6 +233,10 @@
   </si>
   <si>
     <t>Questions by peers and lecturers can be answered correctly and comprehensively. If necessary, questions are answered during the pitch, i.e., there is flexibility in how it is presented without losing focus.</t>
+  </si>
+  <si>
+    <t>Strengths: Very good reproducibility detail. Python version, uv with pyproject.toml, a package table with versions, the module structure (model pipeline, llm pipeline, jev pipeline) and one notebook per rule. Seeds (42), temperature 0, context window 32,768 tokens with a check that the server uses it, max 800 tokens, 120 s timeout, three retries, and the fallback label when no answer can be parsed (115 of 12,084) are all given. Split and prefix counts (914/229 cases, 3,401/1,007 prefixes) and the diagonal covariance choice with its reason are clear, and Appendix A contains the prompt.
+Improvements: (1) Say in which order to run the notebooks, where the BPIC 2011 file is expected, and how long a full run takes. (2) Mention the hardware or server behind Ollama, and note that temperature 0 on a remote server is not guaranteed to give identical output across machines. (3) Say how the JEV API is accessed (key, cost, availability), since this limits reproducibility for others. (4) Clarify typesafe-sdk 0.7.4 (package) versus jev-1.13.0 (model version) in one line. (5) Small typo in 3.3: 'removed form all cases'.</t>
   </si>
 </sst>
 </file>
@@ -994,33 +993,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1030,6 +1007,28 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1386,11 +1385,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="94"/>
       <c r="F1" s="42"/>
       <c r="G1" s="42"/>
       <c r="H1" s="49"/>
@@ -1772,17 +1771,17 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="84"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="88"/>
       <c r="H2" s="17">
         <f>SUM(H3:H8)</f>
         <v>35</v>
@@ -1795,7 +1794,7 @@
       <c r="K2" s="18"/>
     </row>
     <row r="3" spans="1:11" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="92"/>
+      <c r="A3" s="82"/>
       <c r="B3" s="19" t="s">
         <v>25</v>
       </c>
@@ -1823,7 +1822,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="92"/>
+      <c r="A4" s="82"/>
       <c r="B4" s="21" t="s">
         <v>29</v>
       </c>
@@ -1851,7 +1850,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="92"/>
+      <c r="A5" s="82"/>
       <c r="B5" s="21" t="s">
         <v>33</v>
       </c>
@@ -1875,22 +1874,22 @@
         <v>2.7</v>
       </c>
       <c r="K5" s="78" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="82"/>
+      <c r="B6" s="21" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="92"/>
-      <c r="B6" s="21" t="s">
+      <c r="C6" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
       <c r="G6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H6" s="1">
         <v>10</v>
@@ -1903,18 +1902,18 @@
       <c r="K6" s="23"/>
     </row>
     <row r="7" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="92"/>
+      <c r="A7" s="82"/>
       <c r="B7" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
       <c r="G7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H7" s="1">
         <v>4</v>
@@ -1927,18 +1926,18 @@
       <c r="K7" s="23"/>
     </row>
     <row r="8" spans="1:11" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="93"/>
+      <c r="A8" s="83"/>
       <c r="B8" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>42</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>43</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
       <c r="G8" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H8" s="26">
         <v>4</v>
@@ -1951,20 +1950,20 @@
       <c r="K8" s="28"/>
     </row>
     <row r="9" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="94"/>
-      <c r="B9" s="89"/>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
+      <c r="A9" s="84"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
       <c r="H9" s="40"/>
       <c r="I9" s="39"/>
       <c r="J9" s="39"/>
       <c r="K9" s="42"/>
     </row>
     <row r="10" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="86"/>
+      <c r="A10" s="80"/>
       <c r="B10" s="5"/>
       <c r="C10" s="45"/>
       <c r="D10" s="41"/>
@@ -1977,7 +1976,7 @@
       <c r="K10" s="42"/>
     </row>
     <row r="11" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="86"/>
+      <c r="A11" s="80"/>
       <c r="B11" s="5"/>
       <c r="C11" s="43"/>
       <c r="D11" s="5"/>
@@ -1990,7 +1989,7 @@
       <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="86"/>
+      <c r="A12" s="80"/>
       <c r="B12" s="5"/>
       <c r="C12" s="43"/>
       <c r="D12" s="5"/>
@@ -2003,7 +2002,7 @@
       <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="86"/>
+      <c r="A13" s="80"/>
       <c r="B13" s="5"/>
       <c r="C13" s="43"/>
       <c r="D13" s="5"/>
@@ -2016,7 +2015,7 @@
       <c r="K13" s="5"/>
     </row>
     <row r="14" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="86"/>
+      <c r="A14" s="80"/>
       <c r="B14" s="5"/>
       <c r="C14" s="43"/>
       <c r="G14" s="5"/>
@@ -2024,7 +2023,7 @@
       <c r="J14" s="5"/>
     </row>
     <row r="15" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="86"/>
+      <c r="A15" s="80"/>
       <c r="B15" s="5"/>
       <c r="C15" s="43"/>
       <c r="G15" s="5"/>
@@ -2032,7 +2031,7 @@
       <c r="J15" s="5"/>
     </row>
     <row r="16" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="86"/>
+      <c r="A16" s="80"/>
       <c r="B16" s="5"/>
       <c r="C16" s="45"/>
       <c r="D16" s="45"/>
@@ -2046,17 +2045,17 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="85"/>
-      <c r="B17" s="88"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="86"/>
-      <c r="G17" s="86"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="80"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="80"/>
       <c r="H17" s="40"/>
       <c r="J17" s="39"/>
     </row>
     <row r="18" spans="1:10" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="86"/>
+      <c r="A18" s="80"/>
       <c r="B18" s="5"/>
       <c r="C18" s="45"/>
       <c r="G18" s="5"/>
@@ -2064,7 +2063,7 @@
       <c r="J18" s="5"/>
     </row>
     <row r="19" spans="1:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="86"/>
+      <c r="A19" s="80"/>
       <c r="B19" s="5"/>
       <c r="C19" s="45"/>
       <c r="G19" s="5"/>
@@ -2072,7 +2071,7 @@
       <c r="J19" s="5"/>
     </row>
     <row r="20" spans="1:10" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="86"/>
+      <c r="A20" s="80"/>
       <c r="B20" s="5"/>
       <c r="C20" s="45"/>
       <c r="G20" s="5"/>
@@ -2080,7 +2079,7 @@
       <c r="J20" s="5"/>
     </row>
     <row r="21" spans="1:10" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="86"/>
+      <c r="A21" s="80"/>
       <c r="B21" s="5"/>
       <c r="C21" s="45"/>
       <c r="G21" s="5"/>
@@ -2089,17 +2088,17 @@
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="85"/>
-      <c r="B22" s="87"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="86"/>
-      <c r="G22" s="86"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="80"/>
       <c r="H22" s="39"/>
       <c r="J22" s="39"/>
     </row>
     <row r="23" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="86"/>
+      <c r="A23" s="80"/>
       <c r="B23" s="5"/>
       <c r="C23" s="45"/>
       <c r="G23" s="5"/>
@@ -2107,7 +2106,7 @@
       <c r="J23" s="5"/>
     </row>
     <row r="24" spans="1:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="86"/>
+      <c r="A24" s="80"/>
       <c r="B24" s="5"/>
       <c r="C24" s="45"/>
       <c r="G24" s="5"/>
@@ -2115,7 +2114,7 @@
       <c r="J24" s="5"/>
     </row>
     <row r="25" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="86"/>
+      <c r="A25" s="80"/>
       <c r="B25" s="5"/>
       <c r="C25" s="45"/>
       <c r="G25" s="63"/>
@@ -2123,13 +2122,13 @@
       <c r="J25" s="5"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="90"/>
-      <c r="B26" s="86"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
+      <c r="A26" s="79"/>
+      <c r="B26" s="80"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
       <c r="H26" s="40"/>
       <c r="I26" s="47"/>
       <c r="J26" s="48"/>
@@ -2215,17 +2214,17 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="81" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="84"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="88"/>
       <c r="H2" s="29">
         <f>SUM(H3:H9)</f>
         <v>25</v>
@@ -2238,18 +2237,18 @@
       <c r="K2" s="18"/>
     </row>
     <row r="3" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="92"/>
+      <c r="A3" s="82"/>
       <c r="B3" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="35" t="s">
         <v>45</v>
-      </c>
-      <c r="C3" s="35" t="s">
-        <v>46</v>
       </c>
       <c r="D3" s="31"/>
       <c r="E3" s="31"/>
       <c r="F3" s="31"/>
       <c r="G3" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H3" s="36">
         <v>2</v>
@@ -2259,18 +2258,18 @@
       <c r="K3" s="33"/>
     </row>
     <row r="4" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="92"/>
+      <c r="A4" s="82"/>
       <c r="B4" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H4" s="1">
         <v>4</v>
@@ -2283,18 +2282,18 @@
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="92"/>
+      <c r="A5" s="82"/>
       <c r="B5" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H5" s="1">
         <v>4</v>
@@ -2307,18 +2306,18 @@
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="92"/>
+      <c r="A6" s="82"/>
       <c r="B6" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H6" s="1">
         <v>3</v>
@@ -2331,18 +2330,18 @@
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="92"/>
+      <c r="A7" s="82"/>
       <c r="B7" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="D7" s="22"/>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
       <c r="G7" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H7" s="1">
         <v>4</v>
@@ -2355,18 +2354,18 @@
       <c r="K7" s="23"/>
     </row>
     <row r="8" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="92"/>
+      <c r="A8" s="82"/>
       <c r="B8" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H8" s="1">
         <v>3</v>
@@ -2379,18 +2378,18 @@
       <c r="K8" s="23"/>
     </row>
     <row r="9" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="93"/>
+      <c r="A9" s="83"/>
       <c r="B9" s="64" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="65" t="s">
         <v>63</v>
-      </c>
-      <c r="C9" s="65" t="s">
-        <v>64</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
       <c r="F9" s="65"/>
       <c r="G9" s="27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H9" s="66">
         <v>5</v>

--- a/peer review 8/Rubric_Group9_peer_review_DRAFT_v1.xlsx
+++ b/peer review 8/Rubric_Group9_peer_review_DRAFT_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tycho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239E1A3F-1C2B-42C4-A89B-FAC1FAA64433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517A9989-8E34-4433-B90B-F9215369B945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -246,10 +246,10 @@
     <t>Questions by peers and lecturers can be answered correctly and comprehensively. If necessary, questions are answered during the pitch, i.e., there is flexibility in how it is presented without losing focus.</t>
   </si>
   <si>
-    <t>Data and split are described in detail, the evaluation design follows the original study this is good as it helps to motivate the design. The LTL rules which explain the ground truth are not explained in the paper, while reading i could not see for myself why the rules differ in difficulty. The method used to fabricate the ground truth is very reasonable, what could be added is a test of the rule functions on a few hand made traces. It might be worth to add them. Table 2 is clean and easily readable, and the additional ML models without the case attributes add a new angle into the paper. However , the results feel more stated than explained. Some questions I asked while reading the paper : Why does the rule 1 score rise at prefix length 21 specifically?  Why does the LLM over predict the deviant on rule 1 but not on rule 2-4? Why does rule 2 drop so much more then others when case attributes are removed? This circles back to the explaining of the rules, because they give more context to your results and can (maybe?) explain some of the observed results. Some results rely on the confusion matrix like saying the llm often predicts deviant, it could be added to the appendix as there is no way to verify this right now. Lastly, the classifiers use the defaults with no hyperparameter tuning , is this a deliberate choice if so please explain? Maybe tuning the classifiers can generate better results.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Several limitations are stated and follow from the evaluation, like the timing of case attributes. The future work is linked to limitations which is good. Something that could be addes is the lack of hyperparameter tuning, and that some parameters (the 0.5 threshold, minPts) are taken from the original paper which is not bad per se, but should be a noted limitation since other parameters might lead to better results for this specific setting. It is also noted a small model is used for the LLM, future work could therefore also be larger LLM's. The additional ML models without case attributes can maybe also give avenues for future work? </t>
+  </si>
+  <si>
+    <t>Data and split are described in detail, the evaluation design follows the original study this is good as it helps to motivate the design. The LTL rules which explain the ground truth are not explained in the paper, while reading i could not see for myself why the rules differ in difficulty. The method used to fabricate the ground truth is very reasonable, what could be added is a test of the rule functions on a few hand made traces. It might be worth to add them. Table 2 is clean and easily readable, and the additional ML models without the case attributes add a new angle into the paper. However , the results feel more stated than explained. Some questions I asked while reading the paper : Why does the rule 1 score rise at prefix length 21 specifically?  Why does the LLM over predict the deviant on rule 1 but not on rule 2-4? Why does rule 2 drop so much more then others when case attributes are removed? This circles back to the explaining of the rules, because they give more context to your results and can (maybe?) explain some of the observed results. Some results rely on the confusion matrix like saying the llm often predicts deviant, it could be added to the appendix as there is no way to verify this right now. Lastly, the classifiers use the defaults with no hyperparameter tuning , is this a deliberate choice? Maybe tuning the classifiers can generate better results.</t>
   </si>
 </sst>
 </file>
@@ -700,263 +700,263 @@
   </cellStyleXfs>
   <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1154,344 +1154,344 @@
   <dimension ref="A1:K43"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="88.7109375" style="11" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="31.5703125" style="11" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="11" customWidth="1"/>
-    <col min="7" max="7" width="87" style="11" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="11"/>
-    <col min="10" max="10" width="15.85546875" style="11" customWidth="1"/>
-    <col min="11" max="11" width="40.140625" style="11" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="25.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="88.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="31.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="87" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="3"/>
+    <col min="10" max="10" width="15.85546875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="40.140625" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
     </row>
     <row r="2" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="11">
         <v>0.35</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="11">
         <v>0.25</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
+      <c r="D4" s="15"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
     </row>
     <row r="5" spans="1:11" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="11">
         <v>0.3</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
     </row>
     <row r="6" spans="1:11" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="11">
         <v>0.1</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" spans="1:11" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="27" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="28"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
     </row>
     <row r="8" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="29"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="21"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" spans="1:11" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="29"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="21"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
     </row>
     <row r="10" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="12"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="4"/>
     </row>
     <row r="12" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
     </row>
     <row r="13" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
     </row>
     <row r="15" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="J15" s="21"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="J15" s="13"/>
     </row>
     <row r="16" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="J16" s="21"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="13"/>
-      <c r="J18" s="12"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="5"/>
+      <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:11" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="J19" s="21"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" spans="1:11" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="J20" s="21"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:11" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="J21" s="21"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" spans="1:11" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="J22" s="21"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="12"/>
-      <c r="J23" s="12"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="4"/>
+      <c r="J23" s="4"/>
     </row>
     <row r="24" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="J24" s="21"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="J24" s="13"/>
     </row>
     <row r="25" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="J25" s="21"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="21"/>
-      <c r="J26" s="21"/>
+      <c r="A26" s="5"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="13"/>
+      <c r="J26" s="13"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="33"/>
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="25"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C33" s="21"/>
-      <c r="D33" s="29"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="21"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B43" s="34"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1507,438 +1507,438 @@
   <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="11"/>
-    <col min="3" max="3" width="20.7109375" style="11" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="17" style="11" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="11" customWidth="1"/>
-    <col min="7" max="7" width="87" style="11" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="11"/>
-    <col min="10" max="10" width="15.85546875" style="11" customWidth="1"/>
-    <col min="11" max="11" width="110" style="11" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="25.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="3"/>
+    <col min="3" max="3" width="20.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="17" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="87" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="3"/>
+    <col min="10" max="10" width="15.85546875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="110" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="35"/>
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="27"/>
+      <c r="B1" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="H1" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="30" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="39">
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="31">
         <f>SUM(H3:H8)</f>
         <v>35</v>
       </c>
-      <c r="I2" s="40"/>
-      <c r="J2" s="39">
+      <c r="I2" s="32"/>
+      <c r="J2" s="31">
         <f>SUM(J3:J8)</f>
         <v>25.38</v>
       </c>
-      <c r="K2" s="41"/>
+      <c r="K2" s="33"/>
     </row>
     <row r="3" spans="1:11" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="42" t="s">
+      <c r="A3" s="80"/>
+      <c r="B3" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46" t="s">
+      <c r="D3" s="36"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="46">
+      <c r="H3" s="38">
         <v>4</v>
       </c>
-      <c r="I3" s="47">
+      <c r="I3" s="39">
         <v>7</v>
       </c>
-      <c r="J3" s="46">
+      <c r="J3" s="38">
         <f t="shared" ref="J3:J8" si="0">H3*I3/10</f>
         <v>2.8</v>
       </c>
-      <c r="K3" s="48" t="s">
+      <c r="K3" s="40" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="49" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52" t="s">
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="52">
+      <c r="H4" s="44">
         <v>10</v>
       </c>
-      <c r="I4" s="53">
+      <c r="I4" s="45">
         <v>7</v>
       </c>
-      <c r="J4" s="46">
+      <c r="J4" s="38">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K4" s="54" t="s">
+      <c r="K4" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="49" t="s">
+      <c r="A5" s="80"/>
+      <c r="B5" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C5" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="52" t="s">
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="52">
+      <c r="H5" s="44">
         <v>3</v>
       </c>
-      <c r="I5" s="53">
+      <c r="I5" s="45">
         <v>9</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="38">
         <f t="shared" si="0"/>
         <v>2.7</v>
       </c>
-      <c r="K5" s="54" t="s">
+      <c r="K5" s="46" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="49" t="s">
+      <c r="A6" s="80"/>
+      <c r="B6" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="52" t="s">
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="52">
+      <c r="H6" s="44">
         <v>10</v>
       </c>
-      <c r="I6" s="52">
+      <c r="I6" s="44">
         <v>7</v>
       </c>
-      <c r="J6" s="46">
+      <c r="J6" s="38">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K6" s="55" t="s">
-        <v>67</v>
+      <c r="K6" s="47" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
-      <c r="B7" s="49" t="s">
+      <c r="A7" s="80"/>
+      <c r="B7" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="56"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="52" t="s">
+      <c r="D7" s="48"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="44">
         <v>4</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="44">
         <v>6.7</v>
       </c>
-      <c r="J7" s="46">
+      <c r="J7" s="38">
         <f t="shared" si="0"/>
         <v>2.68</v>
       </c>
-      <c r="K7" s="55" t="s">
-        <v>68</v>
+      <c r="K7" s="47" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="57" t="s">
+      <c r="A8" s="80"/>
+      <c r="B8" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="59"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="61" t="s">
+      <c r="D8" s="51"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="61">
+      <c r="H8" s="53">
         <v>4</v>
       </c>
-      <c r="I8" s="61">
+      <c r="I8" s="53">
         <v>8</v>
       </c>
-      <c r="J8" s="62">
+      <c r="J8" s="54">
         <f t="shared" si="0"/>
         <v>3.2</v>
       </c>
-      <c r="K8" s="63" t="s">
+      <c r="K8" s="55" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="66"/>
-      <c r="K9" s="12"/>
+      <c r="A9" s="82"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="4"/>
     </row>
     <row r="10" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="67"/>
-      <c r="K10" s="12"/>
+      <c r="A10" s="82"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="67"/>
-      <c r="K11" s="67"/>
+      <c r="A11" s="82"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
     </row>
     <row r="12" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
+      <c r="A12" s="82"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="57"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="67"/>
-      <c r="K13" s="67"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
     </row>
     <row r="14" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="21"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-      <c r="J14" s="67"/>
+      <c r="A14" s="82"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="13"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="J14" s="57"/>
     </row>
     <row r="15" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="67"/>
-      <c r="C15" s="21"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="J15" s="67"/>
+      <c r="A15" s="82"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="13"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="J15" s="57"/>
     </row>
     <row r="16" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="67"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="67"/>
-      <c r="J16" s="67"/>
-      <c r="K16" s="21"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="13"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="65"/>
-      <c r="J17" s="66"/>
+      <c r="A17" s="77"/>
+      <c r="B17" s="84"/>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="1"/>
+      <c r="J17" s="56"/>
     </row>
     <row r="18" spans="1:10" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="68"/>
-      <c r="G18" s="67"/>
-      <c r="H18" s="67"/>
-      <c r="J18" s="67"/>
+      <c r="A18" s="77"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="58"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="J18" s="57"/>
     </row>
     <row r="19" spans="1:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-      <c r="B19" s="67"/>
-      <c r="C19" s="68"/>
-      <c r="G19" s="67"/>
-      <c r="H19" s="67"/>
-      <c r="J19" s="67"/>
+      <c r="A19" s="77"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="58"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="J19" s="57"/>
     </row>
     <row r="20" spans="1:10" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
-      <c r="B20" s="67"/>
-      <c r="C20" s="68"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="J20" s="67"/>
+      <c r="A20" s="77"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="58"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="J20" s="57"/>
     </row>
     <row r="21" spans="1:10" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="68"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="67"/>
-      <c r="J21" s="67"/>
+      <c r="A21" s="77"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="58"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="J21" s="57"/>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="66"/>
-      <c r="J22" s="66"/>
+      <c r="A22" s="77"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="78"/>
+      <c r="E22" s="78"/>
+      <c r="F22" s="78"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="56"/>
+      <c r="J22" s="56"/>
     </row>
     <row r="23" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="68"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="J23" s="67"/>
+      <c r="A23" s="77"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="58"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="J23" s="57"/>
     </row>
     <row r="24" spans="1:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="68"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="J24" s="67"/>
+      <c r="A24" s="77"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="58"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="J24" s="57"/>
     </row>
     <row r="25" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="68"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="67"/>
-      <c r="J25" s="67"/>
+      <c r="A25" s="77"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="58"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="57"/>
+      <c r="J25" s="57"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="72"/>
+      <c r="A26" s="79"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="79"/>
+      <c r="G26" s="79"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="62"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C32" s="67"/>
-      <c r="D32" s="29"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="21"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="73"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1962,251 +1962,251 @@
   <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="11"/>
-    <col min="3" max="3" width="20.7109375" style="11" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="17" style="11" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="11" customWidth="1"/>
-    <col min="7" max="7" width="87" style="11" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="11"/>
-    <col min="10" max="10" width="15.85546875" style="11" customWidth="1"/>
-    <col min="11" max="11" width="40.140625" style="11" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="25.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="3"/>
+    <col min="3" max="3" width="20.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="17" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="87" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="3"/>
+    <col min="10" max="10" width="15.85546875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="40.140625" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="35"/>
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="27"/>
+      <c r="B1" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="H1" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="30" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="74">
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="64">
         <f>SUM(H3:H9)</f>
         <v>25</v>
       </c>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39">
+      <c r="I2" s="31"/>
+      <c r="J2" s="31">
         <f>SUM(J4:J8)</f>
         <v>0</v>
       </c>
-      <c r="K2" s="41"/>
+      <c r="K2" s="33"/>
     </row>
     <row r="3" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="75" t="s">
+      <c r="A3" s="80"/>
+      <c r="B3" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="78" t="s">
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="79">
+      <c r="H3" s="69">
         <v>2</v>
       </c>
-      <c r="I3" s="80"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="81"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="71"/>
     </row>
     <row r="4" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="49" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52" t="s">
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="52">
+      <c r="H4" s="44">
         <v>4</v>
       </c>
-      <c r="I4" s="52"/>
-      <c r="J4" s="46">
+      <c r="I4" s="44"/>
+      <c r="J4" s="38">
         <f t="shared" ref="J4:J9" si="0">H4*I4/10</f>
         <v>0</v>
       </c>
-      <c r="K4" s="82"/>
+      <c r="K4" s="72"/>
     </row>
     <row r="5" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="49" t="s">
+      <c r="A5" s="80"/>
+      <c r="B5" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C5" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52" t="s">
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="52">
+      <c r="H5" s="44">
         <v>4</v>
       </c>
-      <c r="I5" s="52"/>
-      <c r="J5" s="46">
+      <c r="I5" s="44"/>
+      <c r="J5" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K5" s="82"/>
+      <c r="K5" s="72"/>
     </row>
     <row r="6" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="49" t="s">
+      <c r="A6" s="80"/>
+      <c r="B6" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52" t="s">
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="52">
+      <c r="H6" s="44">
         <v>3</v>
       </c>
-      <c r="I6" s="52"/>
-      <c r="J6" s="46">
+      <c r="I6" s="44"/>
+      <c r="J6" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="82"/>
+      <c r="K6" s="72"/>
     </row>
     <row r="7" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
-      <c r="B7" s="49" t="s">
+      <c r="A7" s="80"/>
+      <c r="B7" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="52" t="s">
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="44">
         <v>4</v>
       </c>
-      <c r="I7" s="51"/>
-      <c r="J7" s="46">
+      <c r="I7" s="43"/>
+      <c r="J7" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K7" s="55"/>
+      <c r="K7" s="47"/>
     </row>
     <row r="8" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="49" t="s">
+      <c r="A8" s="80"/>
+      <c r="B8" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="52" t="s">
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8" s="44">
         <v>3</v>
       </c>
-      <c r="I8" s="51"/>
-      <c r="J8" s="46">
+      <c r="I8" s="43"/>
+      <c r="J8" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="55"/>
+      <c r="K8" s="47"/>
     </row>
     <row r="9" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="83" t="s">
+      <c r="A9" s="80"/>
+      <c r="B9" s="73" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="84" t="s">
+      <c r="C9" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="84"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="62" t="s">
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="85">
+      <c r="H9" s="75">
         <v>5</v>
       </c>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62">
+      <c r="I9" s="54"/>
+      <c r="J9" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K9" s="86"/>
+      <c r="K9" s="76"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C15" s="67"/>
-      <c r="D15" s="29"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="21"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="73"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="2">
